--- a/LuBan/Design/Datas/技能/SkillTransform.xlsx
+++ b/LuBan/Design/Datas/技能/SkillTransform.xlsx
@@ -1160,7 +1160,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.66363636363636" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10" style="6" customWidth="1"/>
     <col min="3" max="3" width="12" style="6" customWidth="1"/>
     <col min="4" max="4" width="19.4545454545455" style="6" customWidth="1"/>
     <col min="5" max="5" width="12.6363636363636" style="6" customWidth="1"/>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="6">
-        <v>101002</v>
+        <v>1001102</v>
       </c>
       <c r="C5" s="6">
-        <v>101002</v>
+        <v>1001102</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>12</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="6">
-        <v>101003</v>
+        <v>1001103</v>
       </c>
       <c r="C6" s="6">
-        <v>101003</v>
+        <v>1001103</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>12</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="6">
-        <v>101004</v>
+        <v>1001104</v>
       </c>
       <c r="C7" s="6">
-        <v>101004</v>
+        <v>1001104</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>12</v>
